--- a/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,16 +313,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -448,7 +448,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -594,19 +594,19 @@
     <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -628,22 +628,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -664,16 +664,16 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
-  </si>
-  <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -722,7 +722,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -747,10 +747,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -774,7 +774,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.id</t>
@@ -792,13 +792,13 @@
     <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.value</t>
@@ -807,10 +807,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.period</t>
@@ -1197,14 +1197,13 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>CombinedMedicationDispense.SupplyEvent.quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationDispense.daysSupply</t>
@@ -1214,6 +1213,15 @@
   </si>
   <si>
     <t>タイミングとして表される投薬量。すなわち、XX日分、XX回分などの数量。</t>
+  </si>
+  <si>
+    <t>effectiveUseTime</t>
+  </si>
+  <si>
+    <t>TQ1.6 Timing/Quantity Segment Service Duration.+Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (Quantity (NM) ^ Units (CWE)), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>
     <t>MedicationDispense.whenPrepared</t>
@@ -1321,7 +1329,10 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>患者が薬をどのように使用するか、または介護者が投与する / How the medication is to be used by the patient or administered by the caregiver</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>投与または速度が行政期間全体で変化することを目的としている場合（例：用量処方の先細り）、さまざまな用量/レートを伝えるために投与量の指示の複数のインスタンスを提供する必要があります。@@ -1829,7 +1840,7 @@
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="94.375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7427,22 +7438,22 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AK48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>380</v>
@@ -7544,16 +7555,16 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>378</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7562,15 +7573,15 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7593,13 +7604,13 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7650,7 +7661,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7668,24 +7679,24 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7708,13 +7719,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7765,7 +7776,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7780,27 +7791,27 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7826,10 +7837,10 @@
         <v>351</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>307</v>
@@ -7882,7 +7893,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7900,24 +7911,24 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7940,13 +7951,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>307</v>
@@ -7999,7 +8010,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8017,13 +8028,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8031,10 +8042,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8057,16 +8068,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8116,7 +8127,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8142,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8143,15 +8154,15 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8174,16 +8185,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8233,7 +8244,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8251,7 +8262,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8265,10 +8276,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8294,10 +8305,10 @@
         <v>325</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8348,7 +8359,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8366,13 +8377,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8380,10 +8391,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8495,10 +8506,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8612,10 +8623,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8731,10 +8742,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8757,13 +8768,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8814,7 +8825,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>89</v>
@@ -8832,7 +8843,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8846,10 +8857,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8875,10 +8886,10 @@
         <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8908,28 +8919,28 @@
         <v>279</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8953,18 +8964,18 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8990,10 +9001,10 @@
         <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9023,28 +9034,28 @@
         <v>279</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9062,13 +9073,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9076,10 +9087,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9102,13 +9113,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>307</v>
@@ -9161,7 +9172,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9179,13 +9190,13 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9193,14 +9204,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9219,16 +9230,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9278,7 +9289,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9296,7 +9307,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9310,10 +9321,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9336,16 +9347,16 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9395,7 +9406,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9413,7 +9424,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1096,10 +1096,10 @@
 </t>
   </si>
   <si>
-    <t>演奏していた個人 / Individual who was performing</t>
-  </si>
-  <si>
-    <t>アクションを実行したデバイス、開業医など。俳優は薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
+    <t>調剤をした個人 / Individual who was performing</t>
+  </si>
+  <si>
+    <t>アクションを実行したデバイス、個人など。調剤した薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -1801,17 +1801,17 @@
   <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.12109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.3125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="246.64453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1820,26 +1820,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="197.484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="62.83984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -646,7 +646,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -740,7 +740,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -887,7 +887,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -911,7 +911,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -921,7 +921,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>医薬品</t>
@@ -941,7 +941,7 @@
     <t>どの物質または製品を分配できるかを特定するコード化された概念。 / A coded concept identifying which substance or product can be dispensed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1009,7 +1009,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1127,7 +1127,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1461,7 +1461,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
